--- a/Data_clean/MCAS/Estados_US/Edos_USA_2016/VERMONT_2016.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2016/VERMONT_2016.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -384,7 +384,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C2">
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -460,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -473,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -486,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -517,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -532,7 +577,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -576,7 +631,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -623,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C19">
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Huamuxtitlán</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -682,7 +762,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nopala de Villagrán</t>
+          <t>Nopala De Villagrán</t>
         </is>
       </c>
       <c r="C23">
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -724,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -755,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Total</t>
@@ -775,7 +870,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C29">
@@ -786,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -799,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Santa María Camotlán</t>
@@ -812,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Santa María Huazolotitlán</t>
@@ -825,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -856,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Hueytamalco</t>
@@ -869,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C36">
@@ -882,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -895,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -908,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -921,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Total</t>
@@ -952,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -978,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -991,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1022,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -1035,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -1048,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -1061,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C50">
@@ -1074,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -1087,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -1100,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Tecolutla</t>
@@ -1113,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -1126,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -1139,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -1152,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -1165,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1188,76 +1413,6 @@
       </c>
       <c r="D59">
         <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 814,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Marzo de 2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
